--- a/jpcore-r4/develop/ValueSet-mhlw-valueset-icd10-2013-jp.xlsx
+++ b/jpcore-r4/develop/ValueSet-mhlw-valueset-icd10-2013-jp.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -24,94 +24,97 @@
     <t>URL</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/ValueSet/ICD10-2013-full</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>1.2.0-dev</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>MHLW_valueSet_icd10_2013_jp</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>MHLW 厚労省ICD102013版</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI)</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>厚労省 2013版 ValueSet http://www.mhlw.go.jp/toukei/sippei</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>厚労省 2013版 http://www.mhlw.go.jp/toukei/sippei</t>
+  </si>
+  <si>
+    <t>Immutable</t>
+  </si>
+  <si>
+    <t>BooleanType[null]</t>
+  </si>
+  <si>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/CodeSystem/ICD10-2013-full</t>
-  </si>
-  <si>
-    <t>Version</t>
-  </si>
-  <si>
-    <t>1.2.0-dev</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>MHLW_valueSet_icd10_2013_jp</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MHLW 厚労省ICD102013版 </t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>active</t>
-  </si>
-  <si>
-    <t>Experimental</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI)</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>厚労省 2013版 ValueSet http://www.mhlw.go.jp/toukei/sippei</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>厚労省 2013版 http://www.mhlw.go.jp/toukei/sippei</t>
-  </si>
-  <si>
-    <t>Immutable</t>
-  </si>
-  <si>
-    <t>BooleanType[null]</t>
-  </si>
-  <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>All codes</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
   </si>
 </sst>
 </file>
@@ -407,7 +410,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/develop/ValueSet-mhlw-valueset-icd10-2013-jp.xlsx
+++ b/jpcore-r4/develop/ValueSet-mhlw-valueset-icd10-2013-jp.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>MHLW 厚労省ICD102013版</t>
+    <t>MHLW 厚生労働省ICD102013版</t>
   </si>
   <si>
     <t>Status</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>厚労省 2013版 ValueSet http://www.mhlw.go.jp/toukei/sippei</t>
+    <t>厚生労働省 2013版 ValueSet http://www.mhlw.go.jp/toukei/sippei</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>厚労省 2013版 http://www.mhlw.go.jp/toukei/sippei</t>
+    <t>厚生労働省 2013版 http://www.mhlw.go.jp/toukei/sippei</t>
   </si>
   <si>
     <t>Immutable</t>
